--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129277971</v>
+        <v>129277969</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tunsjön, Ång</t>
+          <t>Filitjärn, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616282</v>
+        <v>616337</v>
       </c>
       <c r="R3" t="n">
-        <v>6992790</v>
+        <v>6992772</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>10 rosetter</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,32 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129277970</v>
+        <v>129277971</v>
       </c>
       <c r="B4" t="n">
-        <v>80144</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,14 +932,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Filitjärn, Ång</t>
+          <t>Tunsjön, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616340</v>
+        <v>616282</v>
       </c>
       <c r="R4" t="n">
-        <v>6992777</v>
+        <v>6992790</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +981,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>10 rosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129277969</v>
+        <v>129277970</v>
       </c>
       <c r="B5" t="n">
-        <v>91533</v>
+        <v>80144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616337</v>
+        <v>616340</v>
       </c>
       <c r="R5" t="n">
-        <v>6992772</v>
+        <v>6992777</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129277965</v>
+        <v>129277964</v>
       </c>
       <c r="B6" t="n">
-        <v>79071</v>
+        <v>90569</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616340</v>
+        <v>616344</v>
       </c>
       <c r="R6" t="n">
-        <v>6992717</v>
+        <v>6992706</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129277960</v>
+        <v>129277965</v>
       </c>
       <c r="B7" t="n">
-        <v>91818</v>
+        <v>79071</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616399</v>
+        <v>616340</v>
       </c>
       <c r="R7" t="n">
-        <v>6992658</v>
+        <v>6992717</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129277964</v>
+        <v>129277960</v>
       </c>
       <c r="B8" t="n">
-        <v>90562</v>
+        <v>91825</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616344</v>
+        <v>616399</v>
       </c>
       <c r="R8" t="n">
-        <v>6992706</v>
+        <v>6992658</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,32 +1457,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129277967</v>
+        <v>129277966</v>
       </c>
       <c r="B9" t="n">
-        <v>98669</v>
+        <v>82871</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616349</v>
+        <v>616352</v>
       </c>
       <c r="R9" t="n">
-        <v>6992718</v>
+        <v>6992716</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,32 +1568,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129277966</v>
+        <v>129277967</v>
       </c>
       <c r="B10" t="n">
-        <v>82902</v>
+        <v>98676</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616352</v>
+        <v>616349</v>
       </c>
       <c r="R10" t="n">
-        <v>6992716</v>
+        <v>6992718</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1679,32 +1679,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129277974</v>
+        <v>129277973</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>91540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tunsjön, Ång</t>
+          <t>Filitjärn, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>616267</v>
+        <v>616288</v>
       </c>
       <c r="R11" t="n">
-        <v>6992795</v>
+        <v>6992779</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,32 +1790,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129277973</v>
+        <v>129277974</v>
       </c>
       <c r="B12" t="n">
-        <v>91533</v>
+        <v>98676</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1825,14 +1825,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Filitjärn, Ång</t>
+          <t>Tunsjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>616288</v>
+        <v>616267</v>
       </c>
       <c r="R12" t="n">
-        <v>6992779</v>
+        <v>6992795</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,7 +1904,7 @@
         <v>129277975</v>
       </c>
       <c r="B13" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>129277959</v>
       </c>
       <c r="B14" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>129277963</v>
       </c>
       <c r="B15" t="n">
-        <v>91694</v>
+        <v>91701</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>129277972</v>
       </c>
       <c r="B16" t="n">
-        <v>92172</v>
+        <v>92179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>129277968</v>
       </c>
       <c r="B17" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129277977</v>
       </c>
       <c r="B19" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129277961</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129277969</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,32 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129277971</v>
+        <v>129277970</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -932,14 +932,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tunsjön, Ång</t>
+          <t>Filitjärn, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616282</v>
+        <v>616340</v>
       </c>
       <c r="R4" t="n">
-        <v>6992790</v>
+        <v>6992777</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,12 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>10 rosetter</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,32 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129277970</v>
+        <v>129277971</v>
       </c>
       <c r="B5" t="n">
-        <v>80144</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1048,14 +1043,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Filitjärn, Ång</t>
+          <t>Tunsjön, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616340</v>
+        <v>616282</v>
       </c>
       <c r="R5" t="n">
-        <v>6992777</v>
+        <v>6992790</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1087,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1092,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>10 rosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129277964</v>
+        <v>129277965</v>
       </c>
       <c r="B6" t="n">
-        <v>90569</v>
+        <v>79073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616344</v>
+        <v>616340</v>
       </c>
       <c r="R6" t="n">
-        <v>6992706</v>
+        <v>6992717</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129277965</v>
+        <v>129277960</v>
       </c>
       <c r="B7" t="n">
-        <v>79071</v>
+        <v>91827</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616340</v>
+        <v>616399</v>
       </c>
       <c r="R7" t="n">
-        <v>6992717</v>
+        <v>6992658</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129277960</v>
+        <v>129277964</v>
       </c>
       <c r="B8" t="n">
-        <v>91825</v>
+        <v>90571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616399</v>
+        <v>616344</v>
       </c>
       <c r="R8" t="n">
-        <v>6992658</v>
+        <v>6992706</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,32 +1457,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129277966</v>
+        <v>129277967</v>
       </c>
       <c r="B9" t="n">
-        <v>82871</v>
+        <v>98678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616352</v>
+        <v>616349</v>
       </c>
       <c r="R9" t="n">
-        <v>6992716</v>
+        <v>6992718</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,32 +1568,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129277967</v>
+        <v>129277966</v>
       </c>
       <c r="B10" t="n">
-        <v>98676</v>
+        <v>82873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616349</v>
+        <v>616352</v>
       </c>
       <c r="R10" t="n">
-        <v>6992718</v>
+        <v>6992716</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>129277973</v>
       </c>
       <c r="B11" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>129277974</v>
       </c>
       <c r="B12" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>129277975</v>
       </c>
       <c r="B13" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>129277959</v>
       </c>
       <c r="B14" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>129277963</v>
       </c>
       <c r="B15" t="n">
-        <v>91701</v>
+        <v>91703</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>129277972</v>
       </c>
       <c r="B16" t="n">
-        <v>92179</v>
+        <v>92181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>129277968</v>
       </c>
       <c r="B17" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>129277979</v>
       </c>
       <c r="B18" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129277977</v>
       </c>
       <c r="B19" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129277965</v>
+        <v>129277964</v>
       </c>
       <c r="B6" t="n">
-        <v>79073</v>
+        <v>90571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616340</v>
+        <v>616344</v>
       </c>
       <c r="R6" t="n">
-        <v>6992717</v>
+        <v>6992706</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129277960</v>
+        <v>129277965</v>
       </c>
       <c r="B7" t="n">
-        <v>91827</v>
+        <v>79073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616399</v>
+        <v>616340</v>
       </c>
       <c r="R7" t="n">
-        <v>6992658</v>
+        <v>6992717</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129277964</v>
+        <v>129277960</v>
       </c>
       <c r="B8" t="n">
-        <v>90571</v>
+        <v>91827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616344</v>
+        <v>616399</v>
       </c>
       <c r="R8" t="n">
-        <v>6992706</v>
+        <v>6992658</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,32 +1457,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129277967</v>
+        <v>129277966</v>
       </c>
       <c r="B9" t="n">
-        <v>98678</v>
+        <v>82873</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616349</v>
+        <v>616352</v>
       </c>
       <c r="R9" t="n">
-        <v>6992718</v>
+        <v>6992716</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,32 +1568,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129277966</v>
+        <v>129277967</v>
       </c>
       <c r="B10" t="n">
-        <v>82873</v>
+        <v>98678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616352</v>
+        <v>616349</v>
       </c>
       <c r="R10" t="n">
-        <v>6992716</v>
+        <v>6992718</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129277969</v>
+        <v>129277971</v>
       </c>
       <c r="B3" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Filitjärn, Ång</t>
+          <t>Tunsjön, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616337</v>
+        <v>616282</v>
       </c>
       <c r="R3" t="n">
-        <v>6992772</v>
+        <v>6992790</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>10 rosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129277970</v>
+        <v>129277969</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>91542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616340</v>
+        <v>616337</v>
       </c>
       <c r="R4" t="n">
-        <v>6992777</v>
+        <v>6992772</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,32 +1013,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129277971</v>
+        <v>129277970</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1043,14 +1048,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tunsjön, Ång</t>
+          <t>Filitjärn, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616282</v>
+        <v>616340</v>
       </c>
       <c r="R5" t="n">
-        <v>6992790</v>
+        <v>6992777</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,12 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>10 rosetter</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129277971</v>
+        <v>129277969</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tunsjön, Ång</t>
+          <t>Filitjärn, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616282</v>
+        <v>616337</v>
       </c>
       <c r="R3" t="n">
-        <v>6992790</v>
+        <v>6992772</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>10 rosetter</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,32 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129277969</v>
+        <v>129277971</v>
       </c>
       <c r="B4" t="n">
-        <v>91542</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,17 +932,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Filitjärn, Ång</t>
+          <t>Tunsjön, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616337</v>
+        <v>616282</v>
       </c>
       <c r="R4" t="n">
-        <v>6992772</v>
+        <v>6992790</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +981,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>10 rosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129277964</v>
+        <v>129277965</v>
       </c>
       <c r="B6" t="n">
-        <v>90571</v>
+        <v>79073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616344</v>
+        <v>616340</v>
       </c>
       <c r="R6" t="n">
-        <v>6992706</v>
+        <v>6992717</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129277965</v>
+        <v>129277960</v>
       </c>
       <c r="B7" t="n">
-        <v>79073</v>
+        <v>91837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616340</v>
+        <v>616399</v>
       </c>
       <c r="R7" t="n">
-        <v>6992717</v>
+        <v>6992658</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129277960</v>
+        <v>129277964</v>
       </c>
       <c r="B8" t="n">
-        <v>91827</v>
+        <v>90572</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616399</v>
+        <v>616344</v>
       </c>
       <c r="R8" t="n">
-        <v>6992658</v>
+        <v>6992706</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,7 +1571,7 @@
         <v>129277967</v>
       </c>
       <c r="B10" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>129277973</v>
       </c>
       <c r="B11" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>129277974</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>129277975</v>
       </c>
       <c r="B13" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>129277959</v>
       </c>
       <c r="B14" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>129277963</v>
       </c>
       <c r="B15" t="n">
-        <v>91703</v>
+        <v>91712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>129277972</v>
       </c>
       <c r="B16" t="n">
-        <v>92181</v>
+        <v>92196</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>129277968</v>
       </c>
       <c r="B17" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129277977</v>
       </c>
       <c r="B19" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2587,12 +2587,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -897,32 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129277971</v>
+        <v>129277970</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -932,14 +932,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tunsjön, Ång</t>
+          <t>Filitjärn, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616282</v>
+        <v>616340</v>
       </c>
       <c r="R4" t="n">
-        <v>6992790</v>
+        <v>6992777</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,12 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>10 rosetter</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,32 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129277970</v>
+        <v>129277971</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1048,14 +1043,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Filitjärn, Ång</t>
+          <t>Tunsjön, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616340</v>
+        <v>616282</v>
       </c>
       <c r="R5" t="n">
-        <v>6992777</v>
+        <v>6992790</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1087,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1092,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>10 rosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1238,7 +1238,7 @@
         <v>129277960</v>
       </c>
       <c r="B7" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1457,32 +1457,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129277966</v>
+        <v>129277967</v>
       </c>
       <c r="B9" t="n">
-        <v>82873</v>
+        <v>98705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616352</v>
+        <v>616349</v>
       </c>
       <c r="R9" t="n">
-        <v>6992716</v>
+        <v>6992718</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,32 +1568,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129277967</v>
+        <v>129277966</v>
       </c>
       <c r="B10" t="n">
-        <v>98704</v>
+        <v>82873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616349</v>
+        <v>616352</v>
       </c>
       <c r="R10" t="n">
-        <v>6992718</v>
+        <v>6992716</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1679,32 +1679,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129277973</v>
+        <v>129277974</v>
       </c>
       <c r="B11" t="n">
-        <v>91540</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Filitjärn, Ång</t>
+          <t>Tunsjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>616288</v>
+        <v>616267</v>
       </c>
       <c r="R11" t="n">
-        <v>6992779</v>
+        <v>6992795</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,32 +1790,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129277974</v>
+        <v>129277973</v>
       </c>
       <c r="B12" t="n">
-        <v>98704</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1825,14 +1825,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tunsjön, Ång</t>
+          <t>Filitjärn, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>616267</v>
+        <v>616288</v>
       </c>
       <c r="R12" t="n">
-        <v>6992795</v>
+        <v>6992779</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2126,7 +2126,7 @@
         <v>129277963</v>
       </c>
       <c r="B15" t="n">
-        <v>91712</v>
+        <v>91713</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>129277972</v>
       </c>
       <c r="B16" t="n">
-        <v>92196</v>
+        <v>92197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>129277968</v>
       </c>
       <c r="B17" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129277977</v>
       </c>
       <c r="B19" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129277969</v>
+        <v>129277970</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616337</v>
+        <v>616340</v>
       </c>
       <c r="R3" t="n">
-        <v>6992772</v>
+        <v>6992777</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,32 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129277970</v>
+        <v>129277971</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -932,14 +932,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Filitjärn, Ång</t>
+          <t>Tunsjön, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616340</v>
+        <v>616282</v>
       </c>
       <c r="R4" t="n">
-        <v>6992777</v>
+        <v>6992790</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>10 rosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,32 +1013,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129277971</v>
+        <v>129277969</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>91540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1043,17 +1048,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tunsjön, Ång</t>
+          <t>Filitjärn, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616282</v>
+        <v>616337</v>
       </c>
       <c r="R5" t="n">
-        <v>6992790</v>
+        <v>6992772</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,12 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>10 rosetter</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129277965</v>
+        <v>129277964</v>
       </c>
       <c r="B6" t="n">
-        <v>79073</v>
+        <v>90572</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616340</v>
+        <v>616344</v>
       </c>
       <c r="R6" t="n">
-        <v>6992717</v>
+        <v>6992706</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129277960</v>
+        <v>129277965</v>
       </c>
       <c r="B7" t="n">
-        <v>91838</v>
+        <v>79073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616399</v>
+        <v>616340</v>
       </c>
       <c r="R7" t="n">
-        <v>6992658</v>
+        <v>6992717</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129277964</v>
+        <v>129277960</v>
       </c>
       <c r="B8" t="n">
-        <v>90572</v>
+        <v>91838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616344</v>
+        <v>616399</v>
       </c>
       <c r="R8" t="n">
-        <v>6992706</v>
+        <v>6992658</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,7 +1460,7 @@
         <v>129277967</v>
       </c>
       <c r="B9" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1679,32 +1679,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129277974</v>
+        <v>129277973</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>91540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tunsjön, Ång</t>
+          <t>Filitjärn, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>616267</v>
+        <v>616288</v>
       </c>
       <c r="R11" t="n">
-        <v>6992795</v>
+        <v>6992779</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,32 +1790,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129277973</v>
+        <v>129277974</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>98706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1825,14 +1825,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Filitjärn, Ång</t>
+          <t>Tunsjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>616288</v>
+        <v>616267</v>
       </c>
       <c r="R12" t="n">
-        <v>6992779</v>
+        <v>6992795</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129277961</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129277970</v>
+        <v>129277969</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>91543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616340</v>
+        <v>616337</v>
       </c>
       <c r="R3" t="n">
-        <v>6992777</v>
+        <v>6992772</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,32 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129277971</v>
+        <v>129277970</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>80148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -932,14 +932,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tunsjön, Ång</t>
+          <t>Filitjärn, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616282</v>
+        <v>616340</v>
       </c>
       <c r="R4" t="n">
-        <v>6992790</v>
+        <v>6992777</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,12 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>10 rosetter</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,32 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129277969</v>
+        <v>129277971</v>
       </c>
       <c r="B5" t="n">
-        <v>91540</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1048,17 +1043,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Filitjärn, Ång</t>
+          <t>Tunsjön, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616337</v>
+        <v>616282</v>
       </c>
       <c r="R5" t="n">
-        <v>6992772</v>
+        <v>6992790</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1092,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>10 rosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1127,7 @@
         <v>129277964</v>
       </c>
       <c r="B6" t="n">
-        <v>90572</v>
+        <v>90575</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>129277965</v>
       </c>
       <c r="B7" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>129277960</v>
       </c>
       <c r="B8" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,32 +1457,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129277967</v>
+        <v>129277966</v>
       </c>
       <c r="B9" t="n">
-        <v>98706</v>
+        <v>82877</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616349</v>
+        <v>616352</v>
       </c>
       <c r="R9" t="n">
-        <v>6992718</v>
+        <v>6992716</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,32 +1568,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129277966</v>
+        <v>129277967</v>
       </c>
       <c r="B10" t="n">
-        <v>82873</v>
+        <v>98710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616352</v>
+        <v>616349</v>
       </c>
       <c r="R10" t="n">
-        <v>6992716</v>
+        <v>6992718</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>129277973</v>
       </c>
       <c r="B11" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>129277974</v>
       </c>
       <c r="B12" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>129277975</v>
       </c>
       <c r="B13" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>129277959</v>
       </c>
       <c r="B14" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>129277963</v>
       </c>
       <c r="B15" t="n">
-        <v>91713</v>
+        <v>91716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>129277972</v>
       </c>
       <c r="B16" t="n">
-        <v>92197</v>
+        <v>92200</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>129277968</v>
       </c>
       <c r="B17" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129277977</v>
       </c>
       <c r="B19" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129277964</v>
+        <v>129277965</v>
       </c>
       <c r="B6" t="n">
-        <v>90575</v>
+        <v>79075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616344</v>
+        <v>616340</v>
       </c>
       <c r="R6" t="n">
-        <v>6992706</v>
+        <v>6992717</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129277965</v>
+        <v>129277960</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>91841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616340</v>
+        <v>616399</v>
       </c>
       <c r="R7" t="n">
-        <v>6992717</v>
+        <v>6992658</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129277960</v>
+        <v>129277964</v>
       </c>
       <c r="B8" t="n">
-        <v>91841</v>
+        <v>90575</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616399</v>
+        <v>616344</v>
       </c>
       <c r="R8" t="n">
-        <v>6992658</v>
+        <v>6992706</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129277961</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129277969</v>
+        <v>129277970</v>
       </c>
       <c r="B3" t="n">
-        <v>91543</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616337</v>
+        <v>616340</v>
       </c>
       <c r="R3" t="n">
-        <v>6992772</v>
+        <v>6992777</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129277970</v>
+        <v>129277969</v>
       </c>
       <c r="B4" t="n">
-        <v>80148</v>
+        <v>91545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616340</v>
+        <v>616337</v>
       </c>
       <c r="R4" t="n">
-        <v>6992777</v>
+        <v>6992772</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
         <v>129277971</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129277965</v>
+        <v>129277964</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>90577</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616340</v>
+        <v>616344</v>
       </c>
       <c r="R6" t="n">
-        <v>6992717</v>
+        <v>6992706</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129277960</v>
+        <v>129277965</v>
       </c>
       <c r="B7" t="n">
-        <v>91841</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616399</v>
+        <v>616340</v>
       </c>
       <c r="R7" t="n">
-        <v>6992658</v>
+        <v>6992717</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129277964</v>
+        <v>129277960</v>
       </c>
       <c r="B8" t="n">
-        <v>90575</v>
+        <v>91843</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616344</v>
+        <v>616399</v>
       </c>
       <c r="R8" t="n">
-        <v>6992706</v>
+        <v>6992658</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,7 +1460,7 @@
         <v>129277966</v>
       </c>
       <c r="B9" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>129277967</v>
       </c>
       <c r="B10" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>129277973</v>
       </c>
       <c r="B11" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>129277974</v>
       </c>
       <c r="B12" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>129277975</v>
       </c>
       <c r="B13" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>129277959</v>
       </c>
       <c r="B14" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>129277963</v>
       </c>
       <c r="B15" t="n">
-        <v>91716</v>
+        <v>91718</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>129277972</v>
       </c>
       <c r="B16" t="n">
-        <v>92200</v>
+        <v>92202</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>129277968</v>
       </c>
       <c r="B17" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129277977</v>
       </c>
       <c r="B19" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129277970</v>
+        <v>129277969</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>91549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616340</v>
+        <v>616337</v>
       </c>
       <c r="R3" t="n">
-        <v>6992777</v>
+        <v>6992772</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,32 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129277969</v>
+        <v>129277971</v>
       </c>
       <c r="B4" t="n">
-        <v>91545</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -932,17 +932,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Filitjärn, Ång</t>
+          <t>Tunsjön, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616337</v>
+        <v>616282</v>
       </c>
       <c r="R4" t="n">
-        <v>6992772</v>
+        <v>6992790</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>10 rosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,32 +1013,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129277971</v>
+        <v>129277970</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>80149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1043,14 +1048,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tunsjön, Ång</t>
+          <t>Filitjärn, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616282</v>
+        <v>616340</v>
       </c>
       <c r="R5" t="n">
-        <v>6992790</v>
+        <v>6992777</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,12 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>10 rosetter</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129277964</v>
+        <v>129277965</v>
       </c>
       <c r="B6" t="n">
-        <v>90577</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616344</v>
+        <v>616340</v>
       </c>
       <c r="R6" t="n">
-        <v>6992706</v>
+        <v>6992717</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129277965</v>
+        <v>129277960</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>91847</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616340</v>
+        <v>616399</v>
       </c>
       <c r="R7" t="n">
-        <v>6992717</v>
+        <v>6992658</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129277960</v>
+        <v>129277964</v>
       </c>
       <c r="B8" t="n">
-        <v>91843</v>
+        <v>90581</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616399</v>
+        <v>616344</v>
       </c>
       <c r="R8" t="n">
-        <v>6992658</v>
+        <v>6992706</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,7 +1571,7 @@
         <v>129277967</v>
       </c>
       <c r="B10" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>129277973</v>
       </c>
       <c r="B11" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>129277974</v>
       </c>
       <c r="B12" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>129277975</v>
       </c>
       <c r="B13" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>129277959</v>
       </c>
       <c r="B14" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>129277963</v>
       </c>
       <c r="B15" t="n">
-        <v>91718</v>
+        <v>91722</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>129277972</v>
       </c>
       <c r="B16" t="n">
-        <v>92202</v>
+        <v>92206</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>129277968</v>
       </c>
       <c r="B17" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129277977</v>
       </c>
       <c r="B19" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129277969</v>
+        <v>129277971</v>
       </c>
       <c r="B3" t="n">
-        <v>91549</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Filitjärn, Ång</t>
+          <t>Tunsjön, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616337</v>
+        <v>616282</v>
       </c>
       <c r="R3" t="n">
-        <v>6992772</v>
+        <v>6992790</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>10 rosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,32 +902,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129277971</v>
+        <v>129277969</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>91550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -932,17 +937,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tunsjön, Ång</t>
+          <t>Filitjärn, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616282</v>
+        <v>616337</v>
       </c>
       <c r="R4" t="n">
-        <v>6992790</v>
+        <v>6992772</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,12 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>10 rosetter</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1238,7 +1238,7 @@
         <v>129277960</v>
       </c>
       <c r="B7" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>129277964</v>
       </c>
       <c r="B8" t="n">
-        <v>90581</v>
+        <v>90582</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,32 +1457,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129277966</v>
+        <v>129277967</v>
       </c>
       <c r="B9" t="n">
-        <v>82878</v>
+        <v>98724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616352</v>
+        <v>616349</v>
       </c>
       <c r="R9" t="n">
-        <v>6992716</v>
+        <v>6992718</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,32 +1568,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129277967</v>
+        <v>129277966</v>
       </c>
       <c r="B10" t="n">
-        <v>98716</v>
+        <v>82878</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616349</v>
+        <v>616352</v>
       </c>
       <c r="R10" t="n">
-        <v>6992718</v>
+        <v>6992716</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>129277973</v>
       </c>
       <c r="B11" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>129277974</v>
       </c>
       <c r="B12" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>129277975</v>
       </c>
       <c r="B13" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>129277959</v>
       </c>
       <c r="B14" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>129277963</v>
       </c>
       <c r="B15" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>129277972</v>
       </c>
       <c r="B16" t="n">
-        <v>92206</v>
+        <v>92207</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>129277968</v>
       </c>
       <c r="B17" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129277977</v>
       </c>
       <c r="B19" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129277971</v>
+        <v>129277970</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -821,14 +821,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tunsjön, Ång</t>
+          <t>Filitjärn, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616282</v>
+        <v>616340</v>
       </c>
       <c r="R3" t="n">
-        <v>6992790</v>
+        <v>6992777</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>10 rosetter</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,32 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129277969</v>
+        <v>129277971</v>
       </c>
       <c r="B4" t="n">
-        <v>91550</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,17 +932,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Filitjärn, Ång</t>
+          <t>Tunsjön, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616337</v>
+        <v>616282</v>
       </c>
       <c r="R4" t="n">
-        <v>6992772</v>
+        <v>6992790</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +981,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>10 rosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129277970</v>
+        <v>129277969</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>91550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616340</v>
+        <v>616337</v>
       </c>
       <c r="R5" t="n">
-        <v>6992777</v>
+        <v>6992772</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129277965</v>
+        <v>129277964</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>90582</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616340</v>
+        <v>616344</v>
       </c>
       <c r="R6" t="n">
-        <v>6992717</v>
+        <v>6992706</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129277960</v>
+        <v>129277965</v>
       </c>
       <c r="B7" t="n">
-        <v>91848</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616399</v>
+        <v>616340</v>
       </c>
       <c r="R7" t="n">
-        <v>6992658</v>
+        <v>6992717</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129277964</v>
+        <v>129277960</v>
       </c>
       <c r="B8" t="n">
-        <v>90582</v>
+        <v>91848</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616344</v>
+        <v>616399</v>
       </c>
       <c r="R8" t="n">
-        <v>6992706</v>
+        <v>6992658</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,32 +1457,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129277967</v>
+        <v>129277966</v>
       </c>
       <c r="B9" t="n">
-        <v>98724</v>
+        <v>82878</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616349</v>
+        <v>616352</v>
       </c>
       <c r="R9" t="n">
-        <v>6992718</v>
+        <v>6992716</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,32 +1568,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129277966</v>
+        <v>129277967</v>
       </c>
       <c r="B10" t="n">
-        <v>82878</v>
+        <v>98724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616352</v>
+        <v>616349</v>
       </c>
       <c r="R10" t="n">
-        <v>6992716</v>
+        <v>6992718</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129277970</v>
+        <v>129277971</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -821,14 +821,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Filitjärn, Ång</t>
+          <t>Tunsjön, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616340</v>
+        <v>616282</v>
       </c>
       <c r="R3" t="n">
-        <v>6992777</v>
+        <v>6992790</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>10 rosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,32 +902,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129277971</v>
+        <v>129277969</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>91550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -932,17 +937,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tunsjön, Ång</t>
+          <t>Filitjärn, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616282</v>
+        <v>616337</v>
       </c>
       <c r="R4" t="n">
-        <v>6992790</v>
+        <v>6992772</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,12 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>10 rosetter</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129277969</v>
+        <v>129277970</v>
       </c>
       <c r="B5" t="n">
-        <v>91550</v>
+        <v>80149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616337</v>
+        <v>616340</v>
       </c>
       <c r="R5" t="n">
-        <v>6992772</v>
+        <v>6992777</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129277971</v>
+        <v>129277969</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>91553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tunsjön, Ång</t>
+          <t>Filitjärn, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616282</v>
+        <v>616337</v>
       </c>
       <c r="R3" t="n">
-        <v>6992790</v>
+        <v>6992772</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>10 rosetter</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129277969</v>
+        <v>129277970</v>
       </c>
       <c r="B4" t="n">
-        <v>91550</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616337</v>
+        <v>616340</v>
       </c>
       <c r="R4" t="n">
-        <v>6992772</v>
+        <v>6992777</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,32 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129277970</v>
+        <v>129277971</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1048,14 +1043,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Filitjärn, Ång</t>
+          <t>Tunsjön, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616340</v>
+        <v>616282</v>
       </c>
       <c r="R5" t="n">
-        <v>6992777</v>
+        <v>6992790</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1087,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1092,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>10 rosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129277964</v>
+        <v>129277965</v>
       </c>
       <c r="B6" t="n">
-        <v>90582</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616344</v>
+        <v>616340</v>
       </c>
       <c r="R6" t="n">
-        <v>6992706</v>
+        <v>6992717</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129277965</v>
+        <v>129277960</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>91851</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616340</v>
+        <v>616399</v>
       </c>
       <c r="R7" t="n">
-        <v>6992717</v>
+        <v>6992658</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129277960</v>
+        <v>129277964</v>
       </c>
       <c r="B8" t="n">
-        <v>91848</v>
+        <v>90585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616399</v>
+        <v>616344</v>
       </c>
       <c r="R8" t="n">
-        <v>6992658</v>
+        <v>6992706</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,7 +1571,7 @@
         <v>129277967</v>
       </c>
       <c r="B10" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,32 +1679,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129277973</v>
+        <v>129277974</v>
       </c>
       <c r="B11" t="n">
-        <v>91550</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Filitjärn, Ång</t>
+          <t>Tunsjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>616288</v>
+        <v>616267</v>
       </c>
       <c r="R11" t="n">
-        <v>6992779</v>
+        <v>6992795</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,32 +1790,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129277974</v>
+        <v>129277973</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>91553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1825,14 +1825,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tunsjön, Ång</t>
+          <t>Filitjärn, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>616267</v>
+        <v>616288</v>
       </c>
       <c r="R12" t="n">
-        <v>6992795</v>
+        <v>6992779</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,7 +1904,7 @@
         <v>129277975</v>
       </c>
       <c r="B13" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>129277959</v>
       </c>
       <c r="B14" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>129277963</v>
       </c>
       <c r="B15" t="n">
-        <v>91723</v>
+        <v>91726</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>129277972</v>
       </c>
       <c r="B16" t="n">
-        <v>92207</v>
+        <v>92210</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>129277968</v>
       </c>
       <c r="B17" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129277977</v>
       </c>
       <c r="B19" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129277969</v>
+        <v>129277970</v>
       </c>
       <c r="B3" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616337</v>
+        <v>616340</v>
       </c>
       <c r="R3" t="n">
-        <v>6992772</v>
+        <v>6992777</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129277970</v>
+        <v>129277969</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616340</v>
+        <v>616337</v>
       </c>
       <c r="R4" t="n">
-        <v>6992777</v>
+        <v>6992772</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129277960</v>
+        <v>129277964</v>
       </c>
       <c r="B7" t="n">
-        <v>91851</v>
+        <v>90585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616399</v>
+        <v>616344</v>
       </c>
       <c r="R7" t="n">
-        <v>6992658</v>
+        <v>6992706</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129277964</v>
+        <v>129277960</v>
       </c>
       <c r="B8" t="n">
-        <v>90585</v>
+        <v>91851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616344</v>
+        <v>616399</v>
       </c>
       <c r="R8" t="n">
-        <v>6992706</v>
+        <v>6992658</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1679,32 +1679,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129277974</v>
+        <v>129277973</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tunsjön, Ång</t>
+          <t>Filitjärn, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>616267</v>
+        <v>616288</v>
       </c>
       <c r="R11" t="n">
-        <v>6992795</v>
+        <v>6992779</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,32 +1790,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129277973</v>
+        <v>129277974</v>
       </c>
       <c r="B12" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1825,14 +1825,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Filitjärn, Ång</t>
+          <t>Tunsjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>616288</v>
+        <v>616267</v>
       </c>
       <c r="R12" t="n">
-        <v>6992779</v>
+        <v>6992795</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129277970</v>
+        <v>129277969</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616340</v>
+        <v>616337</v>
       </c>
       <c r="R3" t="n">
-        <v>6992777</v>
+        <v>6992772</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129277969</v>
+        <v>129277970</v>
       </c>
       <c r="B4" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616337</v>
+        <v>616340</v>
       </c>
       <c r="R4" t="n">
-        <v>6992772</v>
+        <v>6992777</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129277964</v>
+        <v>129277960</v>
       </c>
       <c r="B7" t="n">
-        <v>90585</v>
+        <v>91851</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616344</v>
+        <v>616399</v>
       </c>
       <c r="R7" t="n">
-        <v>6992706</v>
+        <v>6992658</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129277960</v>
+        <v>129277964</v>
       </c>
       <c r="B8" t="n">
-        <v>91851</v>
+        <v>90585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616399</v>
+        <v>616344</v>
       </c>
       <c r="R8" t="n">
-        <v>6992658</v>
+        <v>6992706</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -1457,32 +1457,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129277966</v>
+        <v>129277967</v>
       </c>
       <c r="B9" t="n">
-        <v>82878</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616352</v>
+        <v>616349</v>
       </c>
       <c r="R9" t="n">
-        <v>6992716</v>
+        <v>6992718</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,32 +1568,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129277967</v>
+        <v>129277966</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>82878</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616349</v>
+        <v>616352</v>
       </c>
       <c r="R10" t="n">
-        <v>6992718</v>
+        <v>6992716</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129277969</v>
+        <v>129277970</v>
       </c>
       <c r="B3" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616337</v>
+        <v>616340</v>
       </c>
       <c r="R3" t="n">
-        <v>6992772</v>
+        <v>6992777</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129277970</v>
+        <v>129277969</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616340</v>
+        <v>616337</v>
       </c>
       <c r="R4" t="n">
-        <v>6992777</v>
+        <v>6992772</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129277960</v>
+        <v>129277964</v>
       </c>
       <c r="B7" t="n">
-        <v>91851</v>
+        <v>90585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616399</v>
+        <v>616344</v>
       </c>
       <c r="R7" t="n">
-        <v>6992658</v>
+        <v>6992706</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129277964</v>
+        <v>129277960</v>
       </c>
       <c r="B8" t="n">
-        <v>90585</v>
+        <v>91851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616344</v>
+        <v>616399</v>
       </c>
       <c r="R8" t="n">
-        <v>6992706</v>
+        <v>6992658</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,32 +1457,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129277967</v>
+        <v>129277966</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>82878</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616349</v>
+        <v>616352</v>
       </c>
       <c r="R9" t="n">
-        <v>6992718</v>
+        <v>6992716</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,32 +1568,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129277966</v>
+        <v>129277967</v>
       </c>
       <c r="B10" t="n">
-        <v>82878</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616352</v>
+        <v>616349</v>
       </c>
       <c r="R10" t="n">
-        <v>6992716</v>
+        <v>6992718</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129277965</v>
+        <v>129277964</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>90585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616340</v>
+        <v>616344</v>
       </c>
       <c r="R6" t="n">
-        <v>6992717</v>
+        <v>6992706</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129277964</v>
+        <v>129277965</v>
       </c>
       <c r="B7" t="n">
-        <v>90585</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616344</v>
+        <v>616340</v>
       </c>
       <c r="R7" t="n">
-        <v>6992706</v>
+        <v>6992717</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1679,32 +1679,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129277973</v>
+        <v>129277974</v>
       </c>
       <c r="B11" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Filitjärn, Ång</t>
+          <t>Tunsjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>616288</v>
+        <v>616267</v>
       </c>
       <c r="R11" t="n">
-        <v>6992779</v>
+        <v>6992795</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,32 +1790,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129277974</v>
+        <v>129277973</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1825,14 +1825,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tunsjön, Ång</t>
+          <t>Filitjärn, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>616267</v>
+        <v>616288</v>
       </c>
       <c r="R12" t="n">
-        <v>6992795</v>
+        <v>6992779</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129277961</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129277970</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129277969</v>
       </c>
       <c r="B4" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129277971</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129277964</v>
+        <v>129277965</v>
       </c>
       <c r="B6" t="n">
-        <v>90585</v>
+        <v>79102</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616344</v>
+        <v>616340</v>
       </c>
       <c r="R6" t="n">
-        <v>6992706</v>
+        <v>6992717</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129277965</v>
+        <v>129277960</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>91879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616340</v>
+        <v>616399</v>
       </c>
       <c r="R7" t="n">
-        <v>6992717</v>
+        <v>6992658</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129277960</v>
+        <v>129277964</v>
       </c>
       <c r="B8" t="n">
-        <v>91851</v>
+        <v>90613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616399</v>
+        <v>616344</v>
       </c>
       <c r="R8" t="n">
-        <v>6992658</v>
+        <v>6992706</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,7 +1460,7 @@
         <v>129277966</v>
       </c>
       <c r="B9" t="n">
-        <v>82878</v>
+        <v>82905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>129277967</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>129277974</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>129277973</v>
       </c>
       <c r="B12" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>129277975</v>
       </c>
       <c r="B13" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>129277959</v>
       </c>
       <c r="B14" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>129277963</v>
       </c>
       <c r="B15" t="n">
-        <v>91726</v>
+        <v>91754</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>129277972</v>
       </c>
       <c r="B16" t="n">
-        <v>92210</v>
+        <v>92238</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>129277968</v>
       </c>
       <c r="B17" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>129277979</v>
       </c>
       <c r="B18" t="n">
-        <v>57831</v>
+        <v>57834</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129277977</v>
       </c>
       <c r="B19" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129277970</v>
+        <v>129277971</v>
       </c>
       <c r="B3" t="n">
-        <v>80175</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -821,14 +821,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Filitjärn, Ång</t>
+          <t>Tunsjön, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616340</v>
+        <v>616282</v>
       </c>
       <c r="R3" t="n">
-        <v>6992777</v>
+        <v>6992790</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>10 rosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1008,32 +1013,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129277971</v>
+        <v>129277970</v>
       </c>
       <c r="B5" t="n">
-        <v>98756</v>
+        <v>80175</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1043,14 +1048,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tunsjön, Ång</t>
+          <t>Filitjärn, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616282</v>
+        <v>616340</v>
       </c>
       <c r="R5" t="n">
-        <v>6992790</v>
+        <v>6992777</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,12 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>10 rosetter</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129277961</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129277971</v>
+        <v>129277969</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>91587</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tunsjön, Ång</t>
+          <t>Filitjärn, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616282</v>
+        <v>616337</v>
       </c>
       <c r="R3" t="n">
-        <v>6992790</v>
+        <v>6992772</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>10 rosetter</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129277969</v>
+        <v>129277970</v>
       </c>
       <c r="B4" t="n">
-        <v>91581</v>
+        <v>80180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616337</v>
+        <v>616340</v>
       </c>
       <c r="R4" t="n">
-        <v>6992772</v>
+        <v>6992777</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,32 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129277970</v>
+        <v>129277971</v>
       </c>
       <c r="B5" t="n">
-        <v>80175</v>
+        <v>98768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1048,14 +1043,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Filitjärn, Ång</t>
+          <t>Tunsjön, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616340</v>
+        <v>616282</v>
       </c>
       <c r="R5" t="n">
-        <v>6992777</v>
+        <v>6992790</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1087,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1092,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>10 rosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1127,7 @@
         <v>129277965</v>
       </c>
       <c r="B6" t="n">
-        <v>79102</v>
+        <v>79107</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>129277960</v>
       </c>
       <c r="B7" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>129277964</v>
       </c>
       <c r="B8" t="n">
-        <v>90613</v>
+        <v>90619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,32 +1457,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129277966</v>
+        <v>129277967</v>
       </c>
       <c r="B9" t="n">
-        <v>82905</v>
+        <v>98768</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616352</v>
+        <v>616349</v>
       </c>
       <c r="R9" t="n">
-        <v>6992716</v>
+        <v>6992718</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,32 +1568,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129277967</v>
+        <v>129277966</v>
       </c>
       <c r="B10" t="n">
-        <v>98756</v>
+        <v>82910</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616349</v>
+        <v>616352</v>
       </c>
       <c r="R10" t="n">
-        <v>6992718</v>
+        <v>6992716</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>129277974</v>
       </c>
       <c r="B11" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>129277973</v>
       </c>
       <c r="B12" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>129277975</v>
       </c>
       <c r="B13" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>129277959</v>
       </c>
       <c r="B14" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>129277963</v>
       </c>
       <c r="B15" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>129277972</v>
       </c>
       <c r="B16" t="n">
-        <v>92238</v>
+        <v>92244</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>129277968</v>
       </c>
       <c r="B17" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>129277979</v>
       </c>
       <c r="B18" t="n">
-        <v>57834</v>
+        <v>57839</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129277977</v>
       </c>
       <c r="B19" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 12277-2021 artfynd.xlsx
+++ b/artfynd/A 12277-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129277961</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129277969</v>
       </c>
       <c r="B3" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129277970</v>
       </c>
       <c r="B4" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129277971</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>129277965</v>
       </c>
       <c r="B6" t="n">
-        <v>79107</v>
+        <v>79108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129277960</v>
+        <v>129277964</v>
       </c>
       <c r="B7" t="n">
-        <v>91885</v>
+        <v>90620</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616399</v>
+        <v>616344</v>
       </c>
       <c r="R7" t="n">
-        <v>6992658</v>
+        <v>6992706</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129277964</v>
+        <v>129277960</v>
       </c>
       <c r="B8" t="n">
-        <v>90619</v>
+        <v>91886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616344</v>
+        <v>616399</v>
       </c>
       <c r="R8" t="n">
-        <v>6992706</v>
+        <v>6992658</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,32 +1457,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129277967</v>
+        <v>129277966</v>
       </c>
       <c r="B9" t="n">
-        <v>98768</v>
+        <v>82911</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616349</v>
+        <v>616352</v>
       </c>
       <c r="R9" t="n">
-        <v>6992718</v>
+        <v>6992716</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,32 +1568,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129277966</v>
+        <v>129277967</v>
       </c>
       <c r="B10" t="n">
-        <v>82910</v>
+        <v>98769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616352</v>
+        <v>616349</v>
       </c>
       <c r="R10" t="n">
-        <v>6992716</v>
+        <v>6992718</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1679,32 +1679,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129277974</v>
+        <v>129277973</v>
       </c>
       <c r="B11" t="n">
-        <v>98768</v>
+        <v>91588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tunsjön, Ång</t>
+          <t>Filitjärn, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>616267</v>
+        <v>616288</v>
       </c>
       <c r="R11" t="n">
-        <v>6992795</v>
+        <v>6992779</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,32 +1790,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129277973</v>
+        <v>129277974</v>
       </c>
       <c r="B12" t="n">
-        <v>91587</v>
+        <v>98769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1825,14 +1825,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Filitjärn, Ång</t>
+          <t>Tunsjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>616288</v>
+        <v>616267</v>
       </c>
       <c r="R12" t="n">
-        <v>6992779</v>
+        <v>6992795</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,7 +1904,7 @@
         <v>129277975</v>
       </c>
       <c r="B13" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>129277959</v>
       </c>
       <c r="B14" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>129277963</v>
       </c>
       <c r="B15" t="n">
-        <v>91760</v>
+        <v>91761</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>129277972</v>
       </c>
       <c r="B16" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>129277968</v>
       </c>
       <c r="B17" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>129277979</v>
       </c>
       <c r="B18" t="n">
-        <v>57839</v>
+        <v>57840</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129277977</v>
       </c>
       <c r="B19" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
